--- a/data/sites.xlsx
+++ b/data/sites.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LICP\code\CIC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526297BC-B664-4DBF-B379-CEBFE5C03D82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4A2A84-67B5-4653-9532-29866DE523C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,8 +24,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{51A17560-F90B-4C56-B812-A7880D38C9D3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+0.654?</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>idx</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,10 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A[m]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>p[hPa]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -118,14 +148,20 @@
     <t>H[m]</t>
   </si>
   <si>
-    <t>rho_ice [g/cm3]</t>
+    <t>DSS</t>
+  </si>
+  <si>
+    <t>A[m ieq]</t>
+  </si>
+  <si>
+    <t>Z[m]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +183,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -451,12 +500,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1">
@@ -470,25 +518,25 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -496,13 +544,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>-12</v>
       </c>
       <c r="D2">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="E2">
         <v>981</v>
@@ -517,11 +565,10 @@
         <v>443</v>
       </c>
       <c r="I2">
-        <f>0.9165*(1-0.000153*C2)</f>
-        <v>0.91818269399999997</v>
+        <v>200</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -529,7 +576,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>-28.9</v>
@@ -550,11 +597,10 @@
         <v>2000</v>
       </c>
       <c r="I3">
-        <f>0.001*920.54</f>
-        <v>0.92054000000000002</v>
+        <v>200</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -562,7 +608,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>-28.9</v>
@@ -583,10 +629,10 @@
         <v>2000</v>
       </c>
       <c r="I4">
-        <v>0.92054000000000002</v>
+        <v>200</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -594,7 +640,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>-19</v>
@@ -615,11 +661,10 @@
         <v>1130</v>
       </c>
       <c r="I5">
-        <f>0.9165*(1-0.000153*C5)</f>
-        <v>0.91916426549999997</v>
+        <v>200</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -627,7 +672,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>-51</v>
@@ -648,11 +693,10 @@
         <v>2742</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I13" si="0">0.9165*(1-0.000153*C6)</f>
-        <v>0.9236514495</v>
+        <v>200</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -660,7 +704,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <v>-49</v>
@@ -681,11 +725,10 @@
         <v>2838</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
-        <v>0.92337100050000009</v>
+        <v>200</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -693,7 +736,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>-54</v>
@@ -714,11 +757,10 @@
         <v>3701</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
-        <v>0.92407212299999997</v>
+        <v>200</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -726,7 +768,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>-39</v>
@@ -747,11 +789,10 @@
         <v>2618</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
-        <v>0.92196875550000001</v>
+        <v>200</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -759,7 +800,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>-31.1</v>
@@ -777,14 +818,13 @@
         <v>0.35</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3085</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
-        <v>0.92086098194999999</v>
+        <v>200</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -792,13 +832,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>-25.4</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>0.13</v>
       </c>
       <c r="E11">
         <v>940</v>
@@ -813,11 +853,10 @@
         <v>993</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
-        <v>0.92006170229999995</v>
+        <v>200</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -825,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>-31.4</v>
@@ -843,14 +882,13 @@
         <v>0.35</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
-        <v>0.92090304929999989</v>
+        <v>200</v>
       </c>
       <c r="J12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -858,7 +896,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13">
         <v>-31</v>
@@ -876,19 +914,51 @@
         <v>0.35</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1796</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
-        <v>0.92084695949999995</v>
+        <v>200</v>
       </c>
       <c r="J13" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>-21</v>
+      </c>
+      <c r="D14">
+        <v>0.16</v>
+      </c>
+      <c r="E14">
+        <v>850</v>
+      </c>
+      <c r="F14">
+        <v>1998</v>
+      </c>
+      <c r="G14">
+        <v>0.35</v>
+      </c>
+      <c r="H14">
+        <v>1236</v>
+      </c>
+      <c r="I14">
+        <v>200</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/sites.xlsx
+++ b/data/sites.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LICP\code\CIC\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LICP\code\SNU\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4A2A84-67B5-4653-9532-29866DE523C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD38732F-52BA-4952-BFB9-85C8987B7A8F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,42 +24,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>User</author>
-  </authors>
-  <commentList>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{51A17560-F90B-4C56-B812-A7880D38C9D3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-0.654?</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>idx</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,14 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T[C]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>p[hPa]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Year</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -149,9 +107,6 @@
   </si>
   <si>
     <t>DSS</t>
-  </si>
-  <si>
-    <t>A[m ieq]</t>
   </si>
   <si>
     <t>Z[m]</t>
@@ -161,7 +116,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,19 +138,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -500,14 +442,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -518,447 +460,320 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>-12</v>
+        <v>2024.1</v>
       </c>
       <c r="D2">
-        <v>1.55</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="E2">
-        <v>981</v>
+        <v>443</v>
       </c>
       <c r="F2">
-        <v>2024.1</v>
-      </c>
-      <c r="G2">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="H2">
-        <v>443</v>
-      </c>
-      <c r="I2">
-        <v>200</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>-28.9</v>
+        <v>2008.54</v>
       </c>
       <c r="D3">
-        <v>0.216</v>
+        <v>0.35</v>
       </c>
       <c r="E3">
-        <v>745</v>
+        <v>2000</v>
       </c>
       <c r="F3">
-        <v>2008.54</v>
-      </c>
-      <c r="G3">
-        <v>0.35</v>
-      </c>
-      <c r="H3">
-        <v>2000</v>
-      </c>
-      <c r="I3">
-        <v>200</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>-28.9</v>
+        <v>2008.54</v>
       </c>
       <c r="D4">
-        <v>0.216</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
-        <v>745</v>
+        <v>2000</v>
       </c>
       <c r="F4">
-        <v>2008.54</v>
-      </c>
-      <c r="G4">
-        <v>0.35</v>
-      </c>
-      <c r="H4">
-        <v>2000</v>
-      </c>
-      <c r="I4">
-        <v>200</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>-19</v>
+        <v>1993</v>
       </c>
       <c r="D5">
-        <v>1.2</v>
+        <v>0.35</v>
       </c>
       <c r="E5">
-        <v>850</v>
+        <v>1130</v>
       </c>
       <c r="F5">
-        <v>1993</v>
-      </c>
-      <c r="G5">
-        <v>0.35</v>
-      </c>
-      <c r="H5">
-        <v>1130</v>
-      </c>
-      <c r="I5">
-        <v>200</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>2000</v>
+      </c>
+      <c r="D6">
+        <v>0.35</v>
+      </c>
+      <c r="E6">
+        <v>2742</v>
+      </c>
+      <c r="F6">
+        <v>200</v>
+      </c>
+      <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>-51</v>
-      </c>
-      <c r="D6">
-        <v>0.08</v>
-      </c>
-      <c r="E6">
-        <v>681</v>
-      </c>
-      <c r="F6">
-        <v>2000</v>
-      </c>
-      <c r="G6">
-        <v>0.35</v>
-      </c>
-      <c r="H6">
-        <v>2742</v>
-      </c>
-      <c r="I6">
-        <v>200</v>
-      </c>
-      <c r="J6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>-49</v>
+        <v>2004</v>
       </c>
       <c r="D7">
-        <v>2.5000000000000001E-2</v>
+        <v>0.35</v>
       </c>
       <c r="E7">
-        <v>677</v>
+        <v>2838</v>
       </c>
       <c r="F7">
-        <v>2004</v>
-      </c>
-      <c r="G7">
-        <v>0.35</v>
-      </c>
-      <c r="H7">
-        <v>2838</v>
-      </c>
-      <c r="I7">
-        <v>200</v>
-      </c>
-      <c r="J7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>-54</v>
+        <v>1999</v>
       </c>
       <c r="D8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.35</v>
       </c>
       <c r="E8">
-        <v>658</v>
+        <v>3701</v>
       </c>
       <c r="F8">
-        <v>1999</v>
-      </c>
-      <c r="G8">
-        <v>0.35</v>
-      </c>
-      <c r="H8">
-        <v>3701</v>
-      </c>
-      <c r="I8">
-        <v>200</v>
-      </c>
-      <c r="J8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>-39</v>
+        <v>1998</v>
       </c>
       <c r="D9">
-        <v>7.0000000000000007E-2</v>
+        <v>0.35</v>
       </c>
       <c r="E9">
-        <v>757</v>
+        <v>2618</v>
       </c>
       <c r="F9">
-        <v>1998</v>
-      </c>
-      <c r="G9">
-        <v>0.35</v>
-      </c>
-      <c r="H9">
-        <v>2618</v>
-      </c>
-      <c r="I9">
-        <v>200</v>
-      </c>
-      <c r="J9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>-31.1</v>
+        <v>2001</v>
       </c>
       <c r="D10">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="E10">
-        <v>691</v>
+        <v>3085</v>
       </c>
       <c r="F10">
-        <v>2001</v>
-      </c>
-      <c r="G10">
-        <v>0.35</v>
-      </c>
-      <c r="H10">
-        <v>3085</v>
-      </c>
-      <c r="I10">
-        <v>200</v>
-      </c>
-      <c r="J10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>-25.4</v>
+        <v>1998</v>
       </c>
       <c r="D11">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="E11">
-        <v>940</v>
+        <v>993</v>
       </c>
       <c r="F11">
-        <v>1998</v>
-      </c>
-      <c r="G11">
-        <v>0.35</v>
-      </c>
-      <c r="H11">
-        <v>993</v>
-      </c>
-      <c r="I11">
-        <v>200</v>
-      </c>
-      <c r="J11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12">
-        <v>-31.4</v>
+        <v>1989</v>
       </c>
       <c r="D12">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="E12">
-        <v>665</v>
+        <v>3100</v>
       </c>
       <c r="F12">
-        <v>1989</v>
-      </c>
-      <c r="G12">
-        <v>0.35</v>
-      </c>
-      <c r="H12">
-        <v>3100</v>
-      </c>
-      <c r="I12">
-        <v>200</v>
-      </c>
-      <c r="J12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>2005</v>
+      </c>
+      <c r="D13">
+        <v>0.35</v>
+      </c>
+      <c r="E13">
+        <v>1796</v>
+      </c>
+      <c r="F13">
+        <v>200</v>
+      </c>
+      <c r="G13" t="s">
         <v>20</v>
       </c>
-      <c r="C13">
-        <v>-31</v>
-      </c>
-      <c r="D13">
-        <v>0.22</v>
-      </c>
-      <c r="E13">
-        <v>799</v>
-      </c>
-      <c r="F13">
-        <v>2005</v>
-      </c>
-      <c r="G13">
-        <v>0.35</v>
-      </c>
-      <c r="H13">
-        <v>1796</v>
-      </c>
-      <c r="I13">
-        <v>200</v>
-      </c>
-      <c r="J13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14">
-        <v>-21</v>
+        <v>1998</v>
       </c>
       <c r="D14">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="E14">
-        <v>850</v>
+        <v>1236</v>
       </c>
       <c r="F14">
-        <v>1998</v>
-      </c>
-      <c r="G14">
-        <v>0.35</v>
-      </c>
-      <c r="H14">
-        <v>1236</v>
-      </c>
-      <c r="I14">
-        <v>200</v>
-      </c>
-      <c r="J14" t="s">
-        <v>22</v>
+        <v>200</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>